--- a/ioub/IRN/Institutions_collaborating_with_Brawijaya_University.xlsx
+++ b/ioub/IRN/Institutions_collaborating_with_Brawijaya_University.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\cahkanor.github.io\ioub\IRN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA97EFC-682C-4CC3-BC5C-EFE53E13B7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45664C95-1C0D-4082-A800-E9F93180A667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11106,7 +11106,7 @@
         <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
